--- a/审核导出/silicone_orange_peel_uv_审核.xlsx
+++ b/审核导出/silicone_orange_peel_uv_审核.xlsx
@@ -748,12 +748,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
